--- a/data/trans_camb/P59A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 10,15</t>
+          <t>-1,84; 9,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,92</t>
+          <t>1,97; 13,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 9,51</t>
+          <t>-2,38; 9,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 11,82</t>
+          <t>1,81; 12,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 12,55</t>
+          <t>2,53; 12,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,52</t>
+          <t>1,72; 10,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,04</t>
+          <t>1,08; 9,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 11,11</t>
+          <t>3,66; 11,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,9</t>
+          <t>0,97; 7,91</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 147,35</t>
+          <t>-16,29; 136,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 204,87</t>
+          <t>10,16; 185,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 134,92</t>
+          <t>-24,74; 123,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 288,13</t>
+          <t>15,51; 338,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,06; 330,46</t>
+          <t>27,67; 318,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,58; 268,66</t>
+          <t>17,09; 270,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 144,87</t>
+          <t>11,32; 157,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 181,89</t>
+          <t>33,31; 189,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 135,73</t>
+          <t>9,44; 134,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,61</t>
+          <t>-1,58; 8,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 10,09</t>
+          <t>0,37; 11,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 10,34</t>
+          <t>-1,53; 10,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 8,83</t>
+          <t>-0,64; 8,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,81</t>
+          <t>2,1; 11,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 11,77</t>
+          <t>2,05; 11,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 7,16</t>
+          <t>0,48; 7,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,64</t>
+          <t>2,34; 9,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,63</t>
+          <t>2,01; 9,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 88,05</t>
+          <t>-11,89; 98,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 105,94</t>
+          <t>1,0; 114,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 113,62</t>
+          <t>-11,33; 114,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 133,14</t>
+          <t>-8,08; 135,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,35; 187,09</t>
+          <t>18,35; 186,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,17; 178,5</t>
+          <t>14,72; 158,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 82,95</t>
+          <t>3,37; 85,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 111,12</t>
+          <t>19,15; 115,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 109,13</t>
+          <t>16,65; 109,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 11,29</t>
+          <t>-2,13; 10,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 10,03</t>
+          <t>-3,02; 9,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 12,19</t>
+          <t>-1,86; 12,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 8,86</t>
+          <t>-2,22; 8,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 7,48</t>
+          <t>-2,74; 7,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 11,74</t>
+          <t>0,97; 12,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 8,11</t>
+          <t>-0,97; 8,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 6,83</t>
+          <t>-1,27; 7,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,34</t>
+          <t>1,51; 10,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 105,64</t>
+          <t>-13,22; 97,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 93,88</t>
+          <t>-18,64; 93,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 110,38</t>
+          <t>-11,11; 115,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 101,1</t>
+          <t>-18,57; 105,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 90,05</t>
+          <t>-21,53; 96,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 141,38</t>
+          <t>4,42; 155,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 79,37</t>
+          <t>-5,86; 80,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 65,75</t>
+          <t>-9,0; 71,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 97,64</t>
+          <t>9,93; 105,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 0,98</t>
+          <t>-8,78; 1,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,49</t>
+          <t>-4,06; 6,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 2,84</t>
+          <t>-7,39; 2,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,3</t>
+          <t>-1,46; 8,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,81</t>
+          <t>-3,42; 5,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 0,68</t>
+          <t>-8,12; 0,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,59</t>
+          <t>-3,27; 3,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 4,05</t>
+          <t>-2,62; 4,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,43</t>
+          <t>-6,74; 0,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 7,24</t>
+          <t>-43,26; 10,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 43,05</t>
+          <t>-20,33; 46,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 20,28</t>
+          <t>-37,17; 18,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 75,12</t>
+          <t>-9,72; 75,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 45,25</t>
+          <t>-23,01; 49,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 6,14</t>
+          <t>-53,62; 4,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 26,59</t>
+          <t>-19,65; 26,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 29,89</t>
+          <t>-15,51; 29,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 3,11</t>
+          <t>-40,17; 1,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,43</t>
+          <t>-1,26; 4,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,69</t>
+          <t>1,02; 6,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,04</t>
+          <t>-0,73; 5,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,58</t>
+          <t>1,47; 6,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,24</t>
+          <t>1,35; 6,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,29</t>
+          <t>0,26; 5,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,84</t>
+          <t>0,97; 4,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,52</t>
+          <t>1,98; 5,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,58</t>
+          <t>0,35; 4,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 35,88</t>
+          <t>-8,68; 35,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,01; 54,02</t>
+          <t>6,58; 55,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 42,66</t>
+          <t>-5,0; 42,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12,17; 73,14</t>
+          <t>13,07; 70,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,29; 69,16</t>
+          <t>9,82; 69,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,15; 58,72</t>
+          <t>2,26; 55,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,45; 43,53</t>
+          <t>8,12; 46,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,71; 50,55</t>
+          <t>15,87; 55,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,71; 41,67</t>
+          <t>2,5; 41,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P59A-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,84</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 9,83</t>
+          <t>-1,53; 10,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 13,61</t>
+          <t>1,64; 14,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 9,08</t>
+          <t>-2,79; 8,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 12,72</t>
+          <t>0,97; 12,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 12,02</t>
+          <t>2,48; 12,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,31</t>
+          <t>1,65; 10,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,49</t>
+          <t>1,41; 9,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,67</t>
+          <t>3,58; 11,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,91</t>
+          <t>1,22; 8,68</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>103,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 136,6</t>
+          <t>-13,92; 145,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 185,0</t>
+          <t>10,41; 187,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 123,02</t>
+          <t>-24,99; 121,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 338,1</t>
+          <t>5,15; 317,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 318,26</t>
+          <t>21,36; 316,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,09; 270,63</t>
+          <t>16,08; 288,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 157,84</t>
+          <t>14,15; 146,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,31; 189,75</t>
+          <t>35,25; 176,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 134,57</t>
+          <t>10,69; 144,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 8,99</t>
+          <t>-1,72; 8,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 11,0</t>
+          <t>-0,22; 10,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 10,65</t>
+          <t>-1,5; 10,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 8,88</t>
+          <t>-0,71; 8,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,91</t>
+          <t>1,86; 11,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,19</t>
+          <t>1,84; 10,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,17</t>
+          <t>0,05; 7,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,7</t>
+          <t>2,63; 10,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,47</t>
+          <t>1,89; 9,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 98,8</t>
+          <t>-11,14; 99,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 114,94</t>
+          <t>-1,85; 109,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 114,61</t>
+          <t>-10,09; 116,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 135,58</t>
+          <t>-7,73; 133,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,35; 186,96</t>
+          <t>13,97; 173,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 158,31</t>
+          <t>12,34; 167,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 85,83</t>
+          <t>0,51; 85,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 115,18</t>
+          <t>22,35; 121,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 109,11</t>
+          <t>15,33; 110,01</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>5,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 10,91</t>
+          <t>-2,33; 11,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,28</t>
+          <t>-4,21; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 12,58</t>
+          <t>-1,2; 12,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 8,88</t>
+          <t>-3,02; 8,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,98</t>
+          <t>-2,78; 7,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 12,75</t>
+          <t>0,65; 11,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,17</t>
+          <t>-0,6; 8,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,34</t>
+          <t>-1,43; 6,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 10,5</t>
+          <t>1,33; 10,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 97,73</t>
+          <t>-14,24; 104,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 93,81</t>
+          <t>-23,94; 83,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 115,18</t>
+          <t>-8,99; 109,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 105,64</t>
+          <t>-21,61; 101,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 96,55</t>
+          <t>-20,28; 97,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 155,5</t>
+          <t>2,69; 138,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 80,79</t>
+          <t>-4,52; 83,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 71,21</t>
+          <t>-10,52; 66,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,93; 105,14</t>
+          <t>6,92; 100,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-1,67</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-1,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,52</t>
+          <t>-8,18; 1,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,82</t>
+          <t>-4,33; 5,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,72</t>
+          <t>-7,38; 3,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 8,22</t>
+          <t>-1,37; 8,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 5,08</t>
+          <t>-4,02; 5,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,49</t>
+          <t>-5,77; 2,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,47</t>
+          <t>-3,65; 3,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,02</t>
+          <t>-2,6; 4,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 0,29</t>
+          <t>-5,23; 1,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-14,02%</t>
+          <t>-10,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-25,33%</t>
+          <t>-12,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,76%</t>
+          <t>-11,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 10,48</t>
+          <t>-41,24; 11,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 46,0</t>
+          <t>-21,24; 41,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 18,23</t>
+          <t>-37,42; 22,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 75,87</t>
+          <t>-9,55; 76,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 49,33</t>
+          <t>-25,5; 46,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 4,62</t>
+          <t>-36,06; 19,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 26,63</t>
+          <t>-21,19; 25,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 29,8</t>
+          <t>-15,79; 30,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 1,94</t>
+          <t>-30,21; 9,17</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,41</t>
+          <t>-1,2; 4,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,86</t>
+          <t>0,95; 6,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,32</t>
+          <t>-0,08; 5,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,43</t>
+          <t>1,18; 6,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,41</t>
+          <t>1,48; 6,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,03</t>
+          <t>1,19; 5,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,89</t>
+          <t>0,82; 4,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,88</t>
+          <t>1,93; 5,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,53</t>
+          <t>1,29; 4,95</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 35,19</t>
+          <t>-8,1; 36,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,58; 55,96</t>
+          <t>6,22; 54,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 42,05</t>
+          <t>-1,15; 46,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,07; 70,5</t>
+          <t>9,89; 71,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,82; 69,39</t>
+          <t>12,48; 68,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,26; 55,72</t>
+          <t>10,21; 66,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,12; 46,17</t>
+          <t>6,21; 41,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,87; 55,81</t>
+          <t>15,01; 51,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,5; 41,15</t>
+          <t>10,47; 45,55</t>
         </is>
       </c>
     </row>
